--- a/f.xlsx
+++ b/f.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -478,11 +478,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Столбец</t>
+          <t>column</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>

--- a/f.xlsx
+++ b/f.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Это</t>
+          <t>This</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/f.xlsx
+++ b/f.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>This</t>
+          <t>qqqqqqqqqqqqq</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/f.xlsx
+++ b/f.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>qqqqqqqqqqqqq</t>
+          <t>This</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -485,7 +485,7 @@
         <v>0.25</v>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/f.xlsx
+++ b/f.xlsx
@@ -425,28 +425,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>col1</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>col2</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>col3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>col4</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
@@ -455,18 +450,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>This</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -474,18 +464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71.52</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="4">
@@ -493,18 +478,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>contains</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+        <v>153.03</v>
       </c>
     </row>
     <row r="5">
@@ -512,18 +492,2757 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>strings.</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68.22</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
+        <v>142.34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>144.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>141.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>136.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>112.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="D11" t="n">
+        <v>120.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>127.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="D13" t="n">
+        <v>114.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>125.61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>67.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>122.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>116.09</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="D17" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>129.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>142.97</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>137.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="D21" t="n">
+        <v>124.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="D22" t="n">
+        <v>141.28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="D23" t="n">
+        <v>143.54</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="D24" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="D25" t="n">
+        <v>129.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>67.63</v>
+      </c>
+      <c r="D26" t="n">
+        <v>141.85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>67.20999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>129.72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="D28" t="n">
+        <v>142.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="D29" t="n">
+        <v>131.55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="D30" t="n">
+        <v>108.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="D31" t="n">
+        <v>113.89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="D32" t="n">
+        <v>103.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="D33" t="n">
+        <v>120.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="D34" t="n">
+        <v>125.79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>136.22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>140.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>128.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>141.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="D39" t="n">
+        <v>121.23</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="D40" t="n">
+        <v>131.35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>106.71</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="D42" t="n">
+        <v>124.36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="D43" t="n">
+        <v>124.86</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="D44" t="n">
+        <v>139.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="n">
+        <v>67.97</v>
+      </c>
+      <c r="D45" t="n">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="D46" t="n">
+        <v>106.45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="D47" t="n">
+        <v>128.76</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="D48" t="n">
+        <v>145.68</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>116.82</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="D50" t="n">
+        <v>143.62</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="n">
+        <v>69.09</v>
+      </c>
+      <c r="D51" t="n">
+        <v>134.93</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="D52" t="n">
+        <v>147.02</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="D53" t="n">
+        <v>126.33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="D54" t="n">
+        <v>125.48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>115.71</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="D56" t="n">
+        <v>123.49</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="D57" t="n">
+        <v>147.89</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="D58" t="n">
+        <v>155.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>128.07</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="D60" t="n">
+        <v>119.37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="D61" t="n">
+        <v>133.81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>128.73</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="n">
+        <v>69</v>
+      </c>
+      <c r="D63" t="n">
+        <v>137.55</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>129.76</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="D65" t="n">
+        <v>128.82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="D66" t="n">
+        <v>135.32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="D67" t="n">
+        <v>109.61</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="n">
+        <v>69.06</v>
+      </c>
+      <c r="D68" t="n">
+        <v>142.47</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="D69" t="n">
+        <v>132.75</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="D70" t="n">
+        <v>103.53</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="D71" t="n">
+        <v>124.73</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="D72" t="n">
+        <v>129.31</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="D73" t="n">
+        <v>134.02</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="D74" t="n">
+        <v>140.4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="D75" t="n">
+        <v>102.84</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="D76" t="n">
+        <v>128.52</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="D77" t="n">
+        <v>120.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="D78" t="n">
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="D79" t="n">
+        <v>132.96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="D80" t="n">
+        <v>115.62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="D81" t="n">
+        <v>122.52</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="D82" t="n">
+        <v>134.63</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="D83" t="n">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="D84" t="n">
+        <v>155.38</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="D85" t="n">
+        <v>128.94</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>129.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="n">
+        <v>69.13</v>
+      </c>
+      <c r="D87" t="n">
+        <v>139.47</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="D88" t="n">
+        <v>140.89</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="D89" t="n">
+        <v>131.59</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="D90" t="n">
+        <v>121.12</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="D91" t="n">
+        <v>131.51</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="D92" t="n">
+        <v>136.55</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="D93" t="n">
+        <v>141.49</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="D94" t="n">
+        <v>140.61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>112.14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="D96" t="n">
+        <v>133.46</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="D97" t="n">
+        <v>131.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="D98" t="n">
+        <v>120.03</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98</v>
+      </c>
+      <c r="C99" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="D99" t="n">
+        <v>123.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="D100" t="n">
+        <v>128.14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="D101" t="n">
+        <v>115.48</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="D102" t="n">
+        <v>102.09</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" t="n">
+        <v>67.09</v>
+      </c>
+      <c r="D103" t="n">
+        <v>130.35</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103</v>
+      </c>
+      <c r="C104" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="D104" t="n">
+        <v>134.18</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="D105" t="n">
+        <v>98.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="D106" t="n">
+        <v>114.56</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="D107" t="n">
+        <v>123.49</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="D108" t="n">
+        <v>123.05</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="D109" t="n">
+        <v>126.48</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="D110" t="n">
+        <v>128.42</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>110</v>
+      </c>
+      <c r="C111" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="D111" t="n">
+        <v>127.19</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="D112" t="n">
+        <v>122.06</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="D113" t="n">
+        <v>127.61</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="D114" t="n">
+        <v>131.64</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="D115" t="n">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="D116" t="n">
+        <v>122.04</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="D117" t="n">
+        <v>128.55</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="D118" t="n">
+        <v>132.68</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>136.06</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>115.94</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="D121" t="n">
+        <v>136.9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>119.88</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" t="n">
+        <v>67.20999999999999</v>
+      </c>
+      <c r="D123" t="n">
+        <v>109.01</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="D124" t="n">
+        <v>128.27</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" t="n">
+        <v>68.94</v>
+      </c>
+      <c r="D125" t="n">
+        <v>135.29</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="D126" t="n">
+        <v>106.86</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="D127" t="n">
+        <v>123.29</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>109.51</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>128</v>
+      </c>
+      <c r="C129" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="D129" t="n">
+        <v>119.31</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="D130" t="n">
+        <v>140.24</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="D131" t="n">
+        <v>133.98</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>131</v>
+      </c>
+      <c r="C132" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="D132" t="n">
+        <v>132.58</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="D133" t="n">
+        <v>130.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>133</v>
+      </c>
+      <c r="C134" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>115.56</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>134</v>
+      </c>
+      <c r="C135" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>123.79</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>135</v>
+      </c>
+      <c r="C136" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>128.14</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>136</v>
+      </c>
+      <c r="C137" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="D137" t="n">
+        <v>135.96</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>137</v>
+      </c>
+      <c r="C138" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="D138" t="n">
+        <v>116.63</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>138</v>
+      </c>
+      <c r="C139" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="D139" t="n">
+        <v>126.82</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>139</v>
+      </c>
+      <c r="C140" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>151.39</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>140</v>
+      </c>
+      <c r="C141" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="D141" t="n">
+        <v>130.4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>141</v>
+      </c>
+      <c r="C142" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="D142" t="n">
+        <v>136.21</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>113.4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>143</v>
+      </c>
+      <c r="C144" t="n">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="D144" t="n">
+        <v>125.33</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>144</v>
+      </c>
+      <c r="C145" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="D145" t="n">
+        <v>127.58</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>145</v>
+      </c>
+      <c r="C146" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="D146" t="n">
+        <v>107.16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>146</v>
+      </c>
+      <c r="C147" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="D147" t="n">
+        <v>116.46</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>147</v>
+      </c>
+      <c r="C148" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="D148" t="n">
+        <v>133.84</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>148</v>
+      </c>
+      <c r="C149" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>112.89</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>149</v>
+      </c>
+      <c r="C150" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="D150" t="n">
+        <v>130.76</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>150</v>
+      </c>
+      <c r="C151" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="D151" t="n">
+        <v>137.76</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>151</v>
+      </c>
+      <c r="C152" t="n">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="D152" t="n">
+        <v>125.4</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>152</v>
+      </c>
+      <c r="C153" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="D153" t="n">
+        <v>138.47</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>153</v>
+      </c>
+      <c r="C154" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="D154" t="n">
+        <v>120.82</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>154</v>
+      </c>
+      <c r="C155" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="D155" t="n">
+        <v>140.15</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>155</v>
+      </c>
+      <c r="C156" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="D156" t="n">
+        <v>136.74</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>156</v>
+      </c>
+      <c r="C157" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="D157" t="n">
+        <v>106.11</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>157</v>
+      </c>
+      <c r="C158" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="D158" t="n">
+        <v>158.96</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>158</v>
+      </c>
+      <c r="C159" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="D159" t="n">
+        <v>108.79</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>159</v>
+      </c>
+      <c r="C160" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="D160" t="n">
+        <v>138.78</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="D161" t="n">
+        <v>115.91</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>161</v>
+      </c>
+      <c r="C162" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="D162" t="n">
+        <v>146.29</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>162</v>
+      </c>
+      <c r="C163" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="D163" t="n">
+        <v>109.88</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>163</v>
+      </c>
+      <c r="C164" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="D164" t="n">
+        <v>139.05</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>164</v>
+      </c>
+      <c r="C165" t="n">
+        <v>68.38</v>
+      </c>
+      <c r="D165" t="n">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>165</v>
+      </c>
+      <c r="C166" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="D166" t="n">
+        <v>128.31</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>166</v>
+      </c>
+      <c r="C167" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="D167" t="n">
+        <v>127.24</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>167</v>
+      </c>
+      <c r="C168" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="D168" t="n">
+        <v>115.23</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>168</v>
+      </c>
+      <c r="C169" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="D169" t="n">
+        <v>124.8</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>169</v>
+      </c>
+      <c r="C170" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="D170" t="n">
+        <v>126.95</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>170</v>
+      </c>
+      <c r="C171" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="D171" t="n">
+        <v>111.27</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>171</v>
+      </c>
+      <c r="C172" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="D172" t="n">
+        <v>122.61</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>172</v>
+      </c>
+      <c r="C173" t="n">
+        <v>67.97</v>
+      </c>
+      <c r="D173" t="n">
+        <v>124.21</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>173</v>
+      </c>
+      <c r="C174" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="D174" t="n">
+        <v>124.65</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>174</v>
+      </c>
+      <c r="C175" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="D175" t="n">
+        <v>119.52</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>175</v>
+      </c>
+      <c r="C176" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="D176" t="n">
+        <v>139.3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>176</v>
+      </c>
+      <c r="C177" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="D177" t="n">
+        <v>104.83</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>177</v>
+      </c>
+      <c r="C178" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="D178" t="n">
+        <v>123.04</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>178</v>
+      </c>
+      <c r="C179" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="D179" t="n">
+        <v>118.89</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>179</v>
+      </c>
+      <c r="C180" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="D180" t="n">
+        <v>121.49</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>180</v>
+      </c>
+      <c r="C181" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="D181" t="n">
+        <v>119.25</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>181</v>
+      </c>
+      <c r="C182" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="D182" t="n">
+        <v>135.02</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>182</v>
+      </c>
+      <c r="C183" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="D183" t="n">
+        <v>116.23</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>183</v>
+      </c>
+      <c r="C184" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="D184" t="n">
+        <v>109.17</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>184</v>
+      </c>
+      <c r="C185" t="n">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="D185" t="n">
+        <v>124.22</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>185</v>
+      </c>
+      <c r="C186" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="D186" t="n">
+        <v>141.16</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>186</v>
+      </c>
+      <c r="C187" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="D187" t="n">
+        <v>129.15</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>187</v>
+      </c>
+      <c r="C188" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="D188" t="n">
+        <v>127.87</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>188</v>
+      </c>
+      <c r="C189" t="n">
+        <v>66.59</v>
+      </c>
+      <c r="D189" t="n">
+        <v>120.92</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>189</v>
+      </c>
+      <c r="C190" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="D190" t="n">
+        <v>127.65</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>190</v>
+      </c>
+      <c r="C191" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="D191" t="n">
+        <v>101.47</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>191</v>
+      </c>
+      <c r="C192" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="D192" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>192</v>
+      </c>
+      <c r="C193" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="D193" t="n">
+        <v>110.95</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>193</v>
+      </c>
+      <c r="C194" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="D194" t="n">
+        <v>132.86</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>194</v>
+      </c>
+      <c r="C195" t="n">
+        <v>67.41</v>
+      </c>
+      <c r="D195" t="n">
+        <v>146.34</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>195</v>
+      </c>
+      <c r="C196" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="D196" t="n">
+        <v>145.59</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>196</v>
+      </c>
+      <c r="C197" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="D197" t="n">
+        <v>120.84</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>197</v>
+      </c>
+      <c r="C198" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="D198" t="n">
+        <v>115.78</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>198</v>
+      </c>
+      <c r="C199" t="n">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="D199" t="n">
+        <v>128.3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>199</v>
+      </c>
+      <c r="C200" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="D200" t="n">
+        <v>127.47</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>200</v>
+      </c>
+      <c r="C201" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="D201" t="n">
+        <v>127.88</v>
       </c>
     </row>
   </sheetData>

--- a/f.xlsx
+++ b/f.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>Weight</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -453,10 +458,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n">
-        <v>115</v>
+        <v>200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
@@ -472,6 +480,9 @@
       <c r="D3" t="n">
         <v>136.49</v>
       </c>
+      <c r="E3" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -486,6 +497,9 @@
       <c r="D4" t="n">
         <v>153.03</v>
       </c>
+      <c r="E4" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -500,6 +514,9 @@
       <c r="D5" t="n">
         <v>142.34</v>
       </c>
+      <c r="E5" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -514,6 +531,9 @@
       <c r="D6" t="n">
         <v>144.3</v>
       </c>
+      <c r="E6" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -528,6 +548,9 @@
       <c r="D7" t="n">
         <v>123.3</v>
       </c>
+      <c r="E7" t="n">
+        <v>18.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -542,6 +565,9 @@
       <c r="D8" t="n">
         <v>141.49</v>
       </c>
+      <c r="E8" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -556,6 +582,9 @@
       <c r="D9" t="n">
         <v>136.46</v>
       </c>
+      <c r="E9" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -570,6 +599,9 @@
       <c r="D10" t="n">
         <v>112.37</v>
       </c>
+      <c r="E10" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -584,6 +616,9 @@
       <c r="D11" t="n">
         <v>120.67</v>
       </c>
+      <c r="E11" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -598,6 +633,9 @@
       <c r="D12" t="n">
         <v>127.45</v>
       </c>
+      <c r="E12" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -612,6 +650,9 @@
       <c r="D13" t="n">
         <v>114.14</v>
       </c>
+      <c r="E13" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -626,6 +667,9 @@
       <c r="D14" t="n">
         <v>125.61</v>
       </c>
+      <c r="E14" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -640,6 +684,9 @@
       <c r="D15" t="n">
         <v>122.46</v>
       </c>
+      <c r="E15" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -654,6 +701,9 @@
       <c r="D16" t="n">
         <v>116.09</v>
       </c>
+      <c r="E16" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -668,6 +718,9 @@
       <c r="D17" t="n">
         <v>140</v>
       </c>
+      <c r="E17" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -682,6 +735,9 @@
       <c r="D18" t="n">
         <v>129.5</v>
       </c>
+      <c r="E18" t="n">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -696,6 +752,9 @@
       <c r="D19" t="n">
         <v>142.97</v>
       </c>
+      <c r="E19" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -710,6 +769,9 @@
       <c r="D20" t="n">
         <v>137.9</v>
       </c>
+      <c r="E20" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -724,6 +786,9 @@
       <c r="D21" t="n">
         <v>124.04</v>
       </c>
+      <c r="E21" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -738,6 +803,9 @@
       <c r="D22" t="n">
         <v>141.28</v>
       </c>
+      <c r="E22" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -752,6 +820,9 @@
       <c r="D23" t="n">
         <v>143.54</v>
       </c>
+      <c r="E23" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -766,6 +837,9 @@
       <c r="D24" t="n">
         <v>97.90000000000001</v>
       </c>
+      <c r="E24" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -780,6 +854,9 @@
       <c r="D25" t="n">
         <v>129.5</v>
       </c>
+      <c r="E25" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -794,6 +871,9 @@
       <c r="D26" t="n">
         <v>141.85</v>
       </c>
+      <c r="E26" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -808,6 +888,9 @@
       <c r="D27" t="n">
         <v>129.72</v>
       </c>
+      <c r="E27" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -822,6 +905,9 @@
       <c r="D28" t="n">
         <v>142.42</v>
       </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -836,6 +922,9 @@
       <c r="D29" t="n">
         <v>131.55</v>
       </c>
+      <c r="E29" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -850,6 +939,9 @@
       <c r="D30" t="n">
         <v>108.33</v>
       </c>
+      <c r="E30" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -864,6 +956,9 @@
       <c r="D31" t="n">
         <v>113.89</v>
       </c>
+      <c r="E31" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -878,6 +973,9 @@
       <c r="D32" t="n">
         <v>103.3</v>
       </c>
+      <c r="E32" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -892,6 +990,9 @@
       <c r="D33" t="n">
         <v>120.75</v>
       </c>
+      <c r="E33" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -906,6 +1007,9 @@
       <c r="D34" t="n">
         <v>125.79</v>
       </c>
+      <c r="E34" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -920,6 +1024,9 @@
       <c r="D35" t="n">
         <v>136.22</v>
       </c>
+      <c r="E35" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -934,6 +1041,9 @@
       <c r="D36" t="n">
         <v>140.1</v>
       </c>
+      <c r="E36" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -948,6 +1058,9 @@
       <c r="D37" t="n">
         <v>128.75</v>
       </c>
+      <c r="E37" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -962,6 +1075,9 @@
       <c r="D38" t="n">
         <v>141.8</v>
       </c>
+      <c r="E38" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -976,6 +1092,9 @@
       <c r="D39" t="n">
         <v>121.23</v>
       </c>
+      <c r="E39" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -990,6 +1109,9 @@
       <c r="D40" t="n">
         <v>131.35</v>
       </c>
+      <c r="E40" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1004,6 +1126,9 @@
       <c r="D41" t="n">
         <v>106.71</v>
       </c>
+      <c r="E41" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1018,6 +1143,9 @@
       <c r="D42" t="n">
         <v>124.36</v>
       </c>
+      <c r="E42" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1032,6 +1160,9 @@
       <c r="D43" t="n">
         <v>124.86</v>
       </c>
+      <c r="E43" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1046,6 +1177,9 @@
       <c r="D44" t="n">
         <v>139.67</v>
       </c>
+      <c r="E44" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1060,6 +1194,9 @@
       <c r="D45" t="n">
         <v>137.37</v>
       </c>
+      <c r="E45" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1074,6 +1211,9 @@
       <c r="D46" t="n">
         <v>106.45</v>
       </c>
+      <c r="E46" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1088,6 +1228,9 @@
       <c r="D47" t="n">
         <v>128.76</v>
       </c>
+      <c r="E47" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1102,6 +1245,9 @@
       <c r="D48" t="n">
         <v>145.68</v>
       </c>
+      <c r="E48" t="n">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1116,6 +1262,9 @@
       <c r="D49" t="n">
         <v>116.82</v>
       </c>
+      <c r="E49" t="n">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1130,6 +1279,9 @@
       <c r="D50" t="n">
         <v>143.62</v>
       </c>
+      <c r="E50" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1144,6 +1296,9 @@
       <c r="D51" t="n">
         <v>134.93</v>
       </c>
+      <c r="E51" t="n">
+        <v>19.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1158,6 +1313,9 @@
       <c r="D52" t="n">
         <v>147.02</v>
       </c>
+      <c r="E52" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1172,6 +1330,9 @@
       <c r="D53" t="n">
         <v>126.33</v>
       </c>
+      <c r="E53" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1186,6 +1347,9 @@
       <c r="D54" t="n">
         <v>125.48</v>
       </c>
+      <c r="E54" t="n">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1200,6 +1364,9 @@
       <c r="D55" t="n">
         <v>115.71</v>
       </c>
+      <c r="E55" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1214,6 +1381,9 @@
       <c r="D56" t="n">
         <v>123.49</v>
       </c>
+      <c r="E56" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1228,6 +1398,9 @@
       <c r="D57" t="n">
         <v>147.89</v>
       </c>
+      <c r="E57" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1242,6 +1415,9 @@
       <c r="D58" t="n">
         <v>155.9</v>
       </c>
+      <c r="E58" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1256,6 +1432,9 @@
       <c r="D59" t="n">
         <v>128.07</v>
       </c>
+      <c r="E59" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1270,6 +1449,9 @@
       <c r="D60" t="n">
         <v>119.37</v>
       </c>
+      <c r="E60" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1284,6 +1466,9 @@
       <c r="D61" t="n">
         <v>133.81</v>
       </c>
+      <c r="E61" t="n">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1298,6 +1483,9 @@
       <c r="D62" t="n">
         <v>128.73</v>
       </c>
+      <c r="E62" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1312,6 +1500,9 @@
       <c r="D63" t="n">
         <v>137.55</v>
       </c>
+      <c r="E63" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1326,6 +1517,9 @@
       <c r="D64" t="n">
         <v>129.76</v>
       </c>
+      <c r="E64" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1340,6 +1534,9 @@
       <c r="D65" t="n">
         <v>128.82</v>
       </c>
+      <c r="E65" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -1354,6 +1551,9 @@
       <c r="D66" t="n">
         <v>135.32</v>
       </c>
+      <c r="E66" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -1368,6 +1568,9 @@
       <c r="D67" t="n">
         <v>109.61</v>
       </c>
+      <c r="E67" t="n">
+        <v>16.6</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1382,6 +1585,9 @@
       <c r="D68" t="n">
         <v>142.47</v>
       </c>
+      <c r="E68" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -1396,6 +1602,9 @@
       <c r="D69" t="n">
         <v>132.75</v>
       </c>
+      <c r="E69" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -1410,6 +1619,9 @@
       <c r="D70" t="n">
         <v>103.53</v>
       </c>
+      <c r="E70" t="n">
+        <v>16.1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1424,6 +1636,9 @@
       <c r="D71" t="n">
         <v>124.73</v>
       </c>
+      <c r="E71" t="n">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -1438,6 +1653,9 @@
       <c r="D72" t="n">
         <v>129.31</v>
       </c>
+      <c r="E72" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -1452,6 +1670,9 @@
       <c r="D73" t="n">
         <v>134.02</v>
       </c>
+      <c r="E73" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -1466,6 +1687,9 @@
       <c r="D74" t="n">
         <v>140.4</v>
       </c>
+      <c r="E74" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -1480,6 +1704,9 @@
       <c r="D75" t="n">
         <v>102.84</v>
       </c>
+      <c r="E75" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -1494,6 +1721,9 @@
       <c r="D76" t="n">
         <v>128.52</v>
       </c>
+      <c r="E76" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -1508,6 +1738,9 @@
       <c r="D77" t="n">
         <v>120.3</v>
       </c>
+      <c r="E77" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -1522,6 +1755,9 @@
       <c r="D78" t="n">
         <v>138.6</v>
       </c>
+      <c r="E78" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -1536,6 +1772,9 @@
       <c r="D79" t="n">
         <v>132.96</v>
       </c>
+      <c r="E79" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -1550,6 +1789,9 @@
       <c r="D80" t="n">
         <v>115.62</v>
       </c>
+      <c r="E80" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -1564,6 +1806,9 @@
       <c r="D81" t="n">
         <v>122.52</v>
       </c>
+      <c r="E81" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -1578,6 +1823,9 @@
       <c r="D82" t="n">
         <v>134.63</v>
       </c>
+      <c r="E82" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -1592,6 +1840,9 @@
       <c r="D83" t="n">
         <v>121.9</v>
       </c>
+      <c r="E83" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -1606,6 +1857,9 @@
       <c r="D84" t="n">
         <v>155.38</v>
       </c>
+      <c r="E84" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -1620,6 +1874,9 @@
       <c r="D85" t="n">
         <v>128.94</v>
       </c>
+      <c r="E85" t="n">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -1634,6 +1891,9 @@
       <c r="D86" t="n">
         <v>129.1</v>
       </c>
+      <c r="E86" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -1648,6 +1908,9 @@
       <c r="D87" t="n">
         <v>139.47</v>
       </c>
+      <c r="E87" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -1662,6 +1925,9 @@
       <c r="D88" t="n">
         <v>140.89</v>
       </c>
+      <c r="E88" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -1676,6 +1942,9 @@
       <c r="D89" t="n">
         <v>131.59</v>
       </c>
+      <c r="E89" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -1690,6 +1959,9 @@
       <c r="D90" t="n">
         <v>121.12</v>
       </c>
+      <c r="E90" t="n">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -1704,6 +1976,9 @@
       <c r="D91" t="n">
         <v>131.51</v>
       </c>
+      <c r="E91" t="n">
+        <v>19.9</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -1718,6 +1993,9 @@
       <c r="D92" t="n">
         <v>136.55</v>
       </c>
+      <c r="E92" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -1732,6 +2010,9 @@
       <c r="D93" t="n">
         <v>141.49</v>
       </c>
+      <c r="E93" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -1746,6 +2027,9 @@
       <c r="D94" t="n">
         <v>140.61</v>
       </c>
+      <c r="E94" t="n">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -1760,6 +2044,9 @@
       <c r="D95" t="n">
         <v>112.14</v>
       </c>
+      <c r="E95" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -1774,6 +2061,9 @@
       <c r="D96" t="n">
         <v>133.46</v>
       </c>
+      <c r="E96" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -1788,6 +2078,9 @@
       <c r="D97" t="n">
         <v>131.8</v>
       </c>
+      <c r="E97" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -1802,6 +2095,9 @@
       <c r="D98" t="n">
         <v>120.03</v>
       </c>
+      <c r="E98" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -1816,6 +2112,9 @@
       <c r="D99" t="n">
         <v>123.1</v>
       </c>
+      <c r="E99" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -1830,6 +2129,9 @@
       <c r="D100" t="n">
         <v>128.14</v>
       </c>
+      <c r="E100" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -1844,6 +2146,9 @@
       <c r="D101" t="n">
         <v>115.48</v>
       </c>
+      <c r="E101" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -1858,6 +2163,9 @@
       <c r="D102" t="n">
         <v>102.09</v>
       </c>
+      <c r="E102" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -1872,6 +2180,9 @@
       <c r="D103" t="n">
         <v>130.35</v>
       </c>
+      <c r="E103" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -1886,6 +2197,9 @@
       <c r="D104" t="n">
         <v>134.18</v>
       </c>
+      <c r="E104" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -1900,6 +2214,9 @@
       <c r="D105" t="n">
         <v>98.64</v>
       </c>
+      <c r="E105" t="n">
+        <v>16.1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -1914,6 +2231,9 @@
       <c r="D106" t="n">
         <v>114.56</v>
       </c>
+      <c r="E106" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -1928,6 +2248,9 @@
       <c r="D107" t="n">
         <v>123.49</v>
       </c>
+      <c r="E107" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -1942,6 +2265,9 @@
       <c r="D108" t="n">
         <v>123.05</v>
       </c>
+      <c r="E108" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -1956,6 +2282,9 @@
       <c r="D109" t="n">
         <v>126.48</v>
       </c>
+      <c r="E109" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -1970,6 +2299,9 @@
       <c r="D110" t="n">
         <v>128.42</v>
       </c>
+      <c r="E110" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -1984,6 +2316,9 @@
       <c r="D111" t="n">
         <v>127.19</v>
       </c>
+      <c r="E111" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -1998,6 +2333,9 @@
       <c r="D112" t="n">
         <v>122.06</v>
       </c>
+      <c r="E112" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -2012,6 +2350,9 @@
       <c r="D113" t="n">
         <v>127.61</v>
       </c>
+      <c r="E113" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -2026,6 +2367,9 @@
       <c r="D114" t="n">
         <v>131.64</v>
       </c>
+      <c r="E114" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -2040,6 +2384,9 @@
       <c r="D115" t="n">
         <v>111.9</v>
       </c>
+      <c r="E115" t="n">
+        <v>18.1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -2054,6 +2401,9 @@
       <c r="D116" t="n">
         <v>122.04</v>
       </c>
+      <c r="E116" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -2068,6 +2418,9 @@
       <c r="D117" t="n">
         <v>128.55</v>
       </c>
+      <c r="E117" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -2082,6 +2435,9 @@
       <c r="D118" t="n">
         <v>132.68</v>
       </c>
+      <c r="E118" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -2096,6 +2452,9 @@
       <c r="D119" t="n">
         <v>136.06</v>
       </c>
+      <c r="E119" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -2110,6 +2469,9 @@
       <c r="D120" t="n">
         <v>115.94</v>
       </c>
+      <c r="E120" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -2124,6 +2486,9 @@
       <c r="D121" t="n">
         <v>136.9</v>
       </c>
+      <c r="E121" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -2138,6 +2503,9 @@
       <c r="D122" t="n">
         <v>119.88</v>
       </c>
+      <c r="E122" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -2152,6 +2520,9 @@
       <c r="D123" t="n">
         <v>109.01</v>
       </c>
+      <c r="E123" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -2166,6 +2537,9 @@
       <c r="D124" t="n">
         <v>128.27</v>
       </c>
+      <c r="E124" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -2180,6 +2554,9 @@
       <c r="D125" t="n">
         <v>135.29</v>
       </c>
+      <c r="E125" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -2194,6 +2571,9 @@
       <c r="D126" t="n">
         <v>106.86</v>
       </c>
+      <c r="E126" t="n">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -2208,6 +2588,9 @@
       <c r="D127" t="n">
         <v>123.29</v>
       </c>
+      <c r="E127" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -2222,6 +2605,9 @@
       <c r="D128" t="n">
         <v>109.51</v>
       </c>
+      <c r="E128" t="n">
+        <v>17.4</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -2236,6 +2622,9 @@
       <c r="D129" t="n">
         <v>119.31</v>
       </c>
+      <c r="E129" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -2250,6 +2639,9 @@
       <c r="D130" t="n">
         <v>140.24</v>
       </c>
+      <c r="E130" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -2264,6 +2656,9 @@
       <c r="D131" t="n">
         <v>133.98</v>
       </c>
+      <c r="E131" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -2278,6 +2673,9 @@
       <c r="D132" t="n">
         <v>132.58</v>
       </c>
+      <c r="E132" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -2292,6 +2690,9 @@
       <c r="D133" t="n">
         <v>130.7</v>
       </c>
+      <c r="E133" t="n">
+        <v>18.1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -2306,6 +2707,9 @@
       <c r="D134" t="n">
         <v>115.56</v>
       </c>
+      <c r="E134" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -2320,6 +2724,9 @@
       <c r="D135" t="n">
         <v>123.79</v>
       </c>
+      <c r="E135" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -2334,6 +2741,9 @@
       <c r="D136" t="n">
         <v>128.14</v>
       </c>
+      <c r="E136" t="n">
+        <v>17.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -2348,6 +2758,9 @@
       <c r="D137" t="n">
         <v>135.96</v>
       </c>
+      <c r="E137" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -2362,6 +2775,9 @@
       <c r="D138" t="n">
         <v>116.63</v>
       </c>
+      <c r="E138" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -2376,6 +2792,9 @@
       <c r="D139" t="n">
         <v>126.82</v>
       </c>
+      <c r="E139" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -2390,6 +2809,9 @@
       <c r="D140" t="n">
         <v>151.39</v>
       </c>
+      <c r="E140" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -2404,6 +2826,9 @@
       <c r="D141" t="n">
         <v>130.4</v>
       </c>
+      <c r="E141" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -2418,6 +2843,9 @@
       <c r="D142" t="n">
         <v>136.21</v>
       </c>
+      <c r="E142" t="n">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -2432,6 +2860,9 @@
       <c r="D143" t="n">
         <v>113.4</v>
       </c>
+      <c r="E143" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -2446,6 +2877,9 @@
       <c r="D144" t="n">
         <v>125.33</v>
       </c>
+      <c r="E144" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -2460,6 +2894,9 @@
       <c r="D145" t="n">
         <v>127.58</v>
       </c>
+      <c r="E145" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -2474,6 +2911,9 @@
       <c r="D146" t="n">
         <v>107.16</v>
       </c>
+      <c r="E146" t="n">
+        <v>17.7</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -2488,6 +2928,9 @@
       <c r="D147" t="n">
         <v>116.46</v>
       </c>
+      <c r="E147" t="n">
+        <v>17.6</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -2502,6 +2945,9 @@
       <c r="D148" t="n">
         <v>133.84</v>
       </c>
+      <c r="E148" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -2516,6 +2962,9 @@
       <c r="D149" t="n">
         <v>112.89</v>
       </c>
+      <c r="E149" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -2530,6 +2979,9 @@
       <c r="D150" t="n">
         <v>130.76</v>
       </c>
+      <c r="E150" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -2544,6 +2996,9 @@
       <c r="D151" t="n">
         <v>137.76</v>
       </c>
+      <c r="E151" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -2558,6 +3013,9 @@
       <c r="D152" t="n">
         <v>125.4</v>
       </c>
+      <c r="E152" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -2572,6 +3030,9 @@
       <c r="D153" t="n">
         <v>138.47</v>
       </c>
+      <c r="E153" t="n">
+        <v>21.4</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -2586,6 +3047,9 @@
       <c r="D154" t="n">
         <v>120.82</v>
       </c>
+      <c r="E154" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -2600,6 +3064,9 @@
       <c r="D155" t="n">
         <v>140.15</v>
       </c>
+      <c r="E155" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -2614,6 +3081,9 @@
       <c r="D156" t="n">
         <v>136.74</v>
       </c>
+      <c r="E156" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -2628,6 +3098,9 @@
       <c r="D157" t="n">
         <v>106.11</v>
       </c>
+      <c r="E157" t="n">
+        <v>18.1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -2642,6 +3115,9 @@
       <c r="D158" t="n">
         <v>158.96</v>
       </c>
+      <c r="E158" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -2656,6 +3132,9 @@
       <c r="D159" t="n">
         <v>108.79</v>
       </c>
+      <c r="E159" t="n">
+        <v>16.8</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -2670,6 +3149,9 @@
       <c r="D160" t="n">
         <v>138.78</v>
       </c>
+      <c r="E160" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -2684,6 +3166,9 @@
       <c r="D161" t="n">
         <v>115.91</v>
       </c>
+      <c r="E161" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -2698,6 +3183,9 @@
       <c r="D162" t="n">
         <v>146.29</v>
       </c>
+      <c r="E162" t="n">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -2712,6 +3200,9 @@
       <c r="D163" t="n">
         <v>109.88</v>
       </c>
+      <c r="E163" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -2726,6 +3217,9 @@
       <c r="D164" t="n">
         <v>139.05</v>
       </c>
+      <c r="E164" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -2740,6 +3234,9 @@
       <c r="D165" t="n">
         <v>119.9</v>
       </c>
+      <c r="E165" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -2754,6 +3251,9 @@
       <c r="D166" t="n">
         <v>128.31</v>
       </c>
+      <c r="E166" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -2768,6 +3268,9 @@
       <c r="D167" t="n">
         <v>127.24</v>
       </c>
+      <c r="E167" t="n">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -2782,6 +3285,9 @@
       <c r="D168" t="n">
         <v>115.23</v>
       </c>
+      <c r="E168" t="n">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -2796,6 +3302,9 @@
       <c r="D169" t="n">
         <v>124.8</v>
       </c>
+      <c r="E169" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -2810,6 +3319,9 @@
       <c r="D170" t="n">
         <v>126.95</v>
       </c>
+      <c r="E170" t="n">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -2824,6 +3336,9 @@
       <c r="D171" t="n">
         <v>111.27</v>
       </c>
+      <c r="E171" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -2838,6 +3353,9 @@
       <c r="D172" t="n">
         <v>122.61</v>
       </c>
+      <c r="E172" t="n">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -2852,6 +3370,9 @@
       <c r="D173" t="n">
         <v>124.21</v>
       </c>
+      <c r="E173" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -2866,6 +3387,9 @@
       <c r="D174" t="n">
         <v>124.65</v>
       </c>
+      <c r="E174" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -2880,6 +3404,9 @@
       <c r="D175" t="n">
         <v>119.52</v>
       </c>
+      <c r="E175" t="n">
+        <v>19.7</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -2894,6 +3421,9 @@
       <c r="D176" t="n">
         <v>139.3</v>
       </c>
+      <c r="E176" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -2908,6 +3438,9 @@
       <c r="D177" t="n">
         <v>104.83</v>
       </c>
+      <c r="E177" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -2922,6 +3455,9 @@
       <c r="D178" t="n">
         <v>123.04</v>
       </c>
+      <c r="E178" t="n">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -2936,6 +3472,9 @@
       <c r="D179" t="n">
         <v>118.89</v>
       </c>
+      <c r="E179" t="n">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -2950,6 +3489,9 @@
       <c r="D180" t="n">
         <v>121.49</v>
       </c>
+      <c r="E180" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -2964,6 +3506,9 @@
       <c r="D181" t="n">
         <v>119.25</v>
       </c>
+      <c r="E181" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -2978,6 +3523,9 @@
       <c r="D182" t="n">
         <v>135.02</v>
       </c>
+      <c r="E182" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -2992,6 +3540,9 @@
       <c r="D183" t="n">
         <v>116.23</v>
       </c>
+      <c r="E183" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -3006,6 +3557,9 @@
       <c r="D184" t="n">
         <v>109.17</v>
       </c>
+      <c r="E184" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -3020,6 +3574,9 @@
       <c r="D185" t="n">
         <v>124.22</v>
       </c>
+      <c r="E185" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -3034,6 +3591,9 @@
       <c r="D186" t="n">
         <v>141.16</v>
       </c>
+      <c r="E186" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -3048,6 +3608,9 @@
       <c r="D187" t="n">
         <v>129.15</v>
       </c>
+      <c r="E187" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -3062,6 +3625,9 @@
       <c r="D188" t="n">
         <v>127.87</v>
       </c>
+      <c r="E188" t="n">
+        <v>19.1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -3076,6 +3642,9 @@
       <c r="D189" t="n">
         <v>120.92</v>
       </c>
+      <c r="E189" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -3090,6 +3659,9 @@
       <c r="D190" t="n">
         <v>127.65</v>
       </c>
+      <c r="E190" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -3104,6 +3676,9 @@
       <c r="D191" t="n">
         <v>101.47</v>
       </c>
+      <c r="E191" t="n">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -3118,6 +3693,9 @@
       <c r="D192" t="n">
         <v>144.99</v>
       </c>
+      <c r="E192" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -3132,6 +3710,9 @@
       <c r="D193" t="n">
         <v>110.95</v>
       </c>
+      <c r="E193" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -3146,6 +3727,9 @@
       <c r="D194" t="n">
         <v>132.86</v>
       </c>
+      <c r="E194" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -3160,6 +3744,9 @@
       <c r="D195" t="n">
         <v>146.34</v>
       </c>
+      <c r="E195" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -3174,6 +3761,9 @@
       <c r="D196" t="n">
         <v>145.59</v>
       </c>
+      <c r="E196" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -3188,6 +3778,9 @@
       <c r="D197" t="n">
         <v>120.84</v>
       </c>
+      <c r="E197" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -3202,6 +3795,9 @@
       <c r="D198" t="n">
         <v>115.78</v>
       </c>
+      <c r="E198" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -3216,6 +3812,9 @@
       <c r="D199" t="n">
         <v>128.3</v>
       </c>
+      <c r="E199" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -3230,6 +3829,9 @@
       <c r="D200" t="n">
         <v>127.47</v>
       </c>
+      <c r="E200" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -3243,6 +3845,9 @@
       </c>
       <c r="D201" t="n">
         <v>127.88</v>
+      </c>
+      <c r="E201" t="n">
+        <v>17.6</v>
       </c>
     </row>
   </sheetData>

--- a/f.xlsx
+++ b/f.xlsx
@@ -458,13 +458,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3">

--- a/f.xlsx
+++ b/f.xlsx
@@ -458,13 +458,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>8.800000000000001</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="3">

--- a/f.xlsx
+++ b/f.xlsx
@@ -458,13 +458,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>65.78</v>
       </c>
       <c r="D2" t="n">
-        <v>127</v>
+        <v>900</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="3">
@@ -1702,10 +1702,10 @@
         <v>64.29000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>102.84</v>
+        <v>116</v>
       </c>
       <c r="E75" t="n">
-        <v>17.5</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="76">

--- a/f.xlsx
+++ b/f.xlsx
@@ -461,10 +461,10 @@
         <v>65.78</v>
       </c>
       <c r="D2" t="n">
-        <v>900</v>
+        <v>121</v>
       </c>
       <c r="E2" t="n">
-        <v>146.2</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="3">
@@ -478,10 +478,10 @@
         <v>71.52</v>
       </c>
       <c r="D3" t="n">
-        <v>136.49</v>
+        <v>143</v>
       </c>
       <c r="E3" t="n">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="4">
@@ -1702,10 +1702,10 @@
         <v>64.29000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>116</v>
+        <v>102.84</v>
       </c>
       <c r="E75" t="n">
-        <v>19.7</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="76">
